--- a/research/traditional_assets/database/data/kazakhstan/kazakhstan_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/kazakhstan/kazakhstan_bank_money_center.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.154</v>
+        <v>0.2465</v>
       </c>
       <c r="E2">
-        <v>0.4125</v>
+        <v>0.5675</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,82 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>163.1</v>
+        <v>467.2</v>
       </c>
       <c r="L2">
-        <v>0.3713570127504554</v>
+        <v>0.7614080834419819</v>
       </c>
       <c r="M2">
-        <v>124.4</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.1025218394593704</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>0.7627222562844881</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>124.4</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.1025218394593704</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>0.7627222562844881</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>1584.7</v>
+        <v>2364.9</v>
       </c>
       <c r="V2">
-        <v>1.305999670347783</v>
+        <v>2.215155488947171</v>
       </c>
       <c r="W2">
-        <v>0.1627587556963812</v>
+        <v>0.5635421681569336</v>
       </c>
       <c r="X2">
-        <v>0.1118048002856068</v>
+        <v>0.1321504773157805</v>
       </c>
       <c r="Y2">
-        <v>0.05095395541077441</v>
+        <v>0.431391690841153</v>
       </c>
       <c r="Z2">
-        <v>0.3542315425767441</v>
+        <v>0.6253713652072969</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06981546527419491</v>
+        <v>0.1014693313450051</v>
       </c>
       <c r="AC2">
-        <v>-0.06981546527419491</v>
+        <v>-0.1014693313450051</v>
       </c>
       <c r="AD2">
-        <v>1617.1</v>
+        <v>1388.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1617.1</v>
+        <v>1388.3</v>
       </c>
       <c r="AG2">
-        <v>32.40000000000009</v>
+        <v>-976.5999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.5713124889595478</v>
+        <v>0.5652917464066126</v>
       </c>
       <c r="AI2">
-        <v>0.6302272107252817</v>
+        <v>0.5299461770431729</v>
       </c>
       <c r="AJ2">
-        <v>0.02600738481297166</v>
+        <v>-10.7318681318681</v>
       </c>
       <c r="AK2">
-        <v>0.03302079086832459</v>
+        <v>-3.832810047095758</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +707,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.197</v>
+        <v>0.247</v>
       </c>
       <c r="E3">
-        <v>0.544</v>
+        <v>0.499</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,85 +725,82 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>134.4</v>
+        <v>192</v>
       </c>
       <c r="L3">
-        <v>0.4579216354344123</v>
+        <v>0.5534736235226291</v>
       </c>
       <c r="M3">
-        <v>124.4</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.1180153685608576</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.9255952380952381</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>124.4</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.1180153685608576</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.9255952380952381</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>1023.4</v>
+        <v>733.4</v>
       </c>
       <c r="V3">
-        <v>0.970875628498245</v>
+        <v>0.9029795616843141</v>
       </c>
       <c r="W3">
-        <v>0.2301369863013699</v>
+        <v>0.3148057058534186</v>
       </c>
       <c r="X3">
-        <v>0.07807184259095512</v>
+        <v>0.1127149430775625</v>
       </c>
       <c r="Y3">
-        <v>0.1520651437104147</v>
+        <v>0.2020907627758561</v>
       </c>
       <c r="Z3">
-        <v>0.3216438356164383</v>
+        <v>0.5291336180597925</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06404524612412683</v>
+        <v>0.09643279263985791</v>
       </c>
       <c r="AC3">
-        <v>-0.06404524612412683</v>
+        <v>-0.09643279263985791</v>
       </c>
       <c r="AD3">
-        <v>1069.1</v>
+        <v>824.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1069.1</v>
+        <v>824.7</v>
       </c>
       <c r="AG3">
-        <v>45.69999999999993</v>
+        <v>91.30000000000007</v>
       </c>
       <c r="AH3">
-        <v>0.5035324039186134</v>
+        <v>0.5038181929256521</v>
       </c>
       <c r="AI3">
-        <v>0.6367480643240023</v>
+        <v>0.5483742270097746</v>
       </c>
       <c r="AJ3">
-        <v>0.04155300963811597</v>
+        <v>0.1010514665190925</v>
       </c>
       <c r="AK3">
-        <v>0.06970713849908472</v>
+        <v>0.118494484101233</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -832,10 +826,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.111</v>
+        <v>0.246</v>
       </c>
       <c r="E4">
-        <v>0.281</v>
+        <v>0.636</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,10 +844,10 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>28.7</v>
+        <v>275.2</v>
       </c>
       <c r="L4">
-        <v>0.1969800960878517</v>
+        <v>1.031871016122985</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -877,55 +871,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>561.3</v>
+        <v>1631.5</v>
       </c>
       <c r="V4">
-        <v>3.523540489642184</v>
+        <v>6.388018794048551</v>
       </c>
       <c r="W4">
-        <v>0.0953805250913925</v>
+        <v>0.8122786304604486</v>
       </c>
       <c r="X4">
-        <v>0.1455377579802584</v>
+        <v>0.1515860115539986</v>
       </c>
       <c r="Y4">
-        <v>-0.05015723288886592</v>
+        <v>0.6606926189064499</v>
       </c>
       <c r="Z4">
-        <v>0.4450662406412375</v>
+        <v>0.8191610586742921</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.075585684424263</v>
+        <v>0.1065058700501523</v>
       </c>
       <c r="AC4">
-        <v>-0.075585684424263</v>
+        <v>-0.1065058700501523</v>
       </c>
       <c r="AD4">
-        <v>548</v>
+        <v>563.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>548</v>
+        <v>563.6</v>
       </c>
       <c r="AG4">
-        <v>-13.29999999999995</v>
+        <v>-1067.9</v>
       </c>
       <c r="AH4">
-        <v>0.7747773222112259</v>
+        <v>0.6881562881562882</v>
       </c>
       <c r="AI4">
-        <v>0.6178825121208704</v>
+        <v>0.5051084423731851</v>
       </c>
       <c r="AJ4">
-        <v>-0.09109589041095856</v>
+        <v>1.314338461538461</v>
       </c>
       <c r="AK4">
-        <v>-0.04084766584766571</v>
+        <v>2.070777583866589</v>
       </c>
       <c r="AL4">
         <v>0</v>

--- a/research/traditional_assets/database/data/kazakhstan/kazakhstan_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/kazakhstan/kazakhstan_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.2465</v>
+        <v>0.22</v>
       </c>
       <c r="E2">
-        <v>0.5675</v>
+        <v>0.271</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,82 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>467.2</v>
+        <v>228.1</v>
       </c>
       <c r="L2">
-        <v>0.7614080834419819</v>
+        <v>0.5859234523503725</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>102.7</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.1361527243802201</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.4502411223147743</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>102.7</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.1361527243802201</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.4502411223147743</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>2364.9</v>
+        <v>607.2</v>
       </c>
       <c r="V2">
-        <v>2.215155488947171</v>
+        <v>0.8049847540766274</v>
       </c>
       <c r="W2">
-        <v>0.5635421681569336</v>
+        <v>0.3358362779740871</v>
       </c>
       <c r="X2">
-        <v>0.1321504773157805</v>
+        <v>0.09380921991104309</v>
       </c>
       <c r="Y2">
-        <v>0.431391690841153</v>
+        <v>0.242027058063044</v>
       </c>
       <c r="Z2">
-        <v>0.6253713652072969</v>
+        <v>0.5196209289909237</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1014693313450051</v>
+        <v>0.08074069114383371</v>
       </c>
       <c r="AC2">
-        <v>-0.1014693313450051</v>
+        <v>-0.08074069114383371</v>
       </c>
       <c r="AD2">
-        <v>1388.3</v>
+        <v>841.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1388.3</v>
+        <v>841.4</v>
       </c>
       <c r="AG2">
-        <v>-976.5999999999999</v>
+        <v>234.1999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.5652917464066126</v>
+        <v>0.5272920975120637</v>
       </c>
       <c r="AI2">
-        <v>0.5299461770431729</v>
+        <v>0.5054060547813551</v>
       </c>
       <c r="AJ2">
-        <v>-10.7318681318681</v>
+        <v>0.2369246332827516</v>
       </c>
       <c r="AK2">
-        <v>-3.832810047095758</v>
+        <v>0.2214447806354009</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -707,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.247</v>
+        <v>0.22</v>
       </c>
       <c r="E3">
-        <v>0.499</v>
+        <v>0.271</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -725,206 +728,90 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>192</v>
+        <v>228.1</v>
       </c>
       <c r="L3">
-        <v>0.5534736235226291</v>
+        <v>0.5859234523503725</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>102.7</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.1361527243802201</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.4502411223147743</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>102.7</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.1361527243802201</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.4502411223147743</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>733.4</v>
+        <v>607.2</v>
       </c>
       <c r="V3">
-        <v>0.9029795616843141</v>
+        <v>0.8049847540766274</v>
       </c>
       <c r="W3">
-        <v>0.3148057058534186</v>
+        <v>0.3358362779740871</v>
       </c>
       <c r="X3">
-        <v>0.1127149430775625</v>
+        <v>0.09380921991104309</v>
       </c>
       <c r="Y3">
-        <v>0.2020907627758561</v>
+        <v>0.242027058063044</v>
       </c>
       <c r="Z3">
-        <v>0.5291336180597925</v>
+        <v>0.5196209289909237</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.09643279263985791</v>
+        <v>0.08074069114383371</v>
       </c>
       <c r="AC3">
-        <v>-0.09643279263985791</v>
+        <v>-0.08074069114383371</v>
       </c>
       <c r="AD3">
-        <v>824.7</v>
+        <v>841.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>824.7</v>
+        <v>841.4</v>
       </c>
       <c r="AG3">
-        <v>91.30000000000007</v>
+        <v>234.1999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.5038181929256521</v>
+        <v>0.5272920975120637</v>
       </c>
       <c r="AI3">
-        <v>0.5483742270097746</v>
+        <v>0.5054060547813551</v>
       </c>
       <c r="AJ3">
-        <v>0.1010514665190925</v>
+        <v>0.2369246332827516</v>
       </c>
       <c r="AK3">
-        <v>0.118494484101233</v>
+        <v>0.2214447806354009</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Kazakhstan</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Joint Stock Company Bank CenterCredit (KAS:CCBN)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.246</v>
-      </c>
-      <c r="E4">
-        <v>0.636</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>275.2</v>
-      </c>
-      <c r="L4">
-        <v>1.031871016122985</v>
-      </c>
-      <c r="M4">
-        <v>-0</v>
-      </c>
-      <c r="N4">
-        <v>-0</v>
-      </c>
-      <c r="O4">
-        <v>-0</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>-0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>1631.5</v>
-      </c>
-      <c r="V4">
-        <v>6.388018794048551</v>
-      </c>
-      <c r="W4">
-        <v>0.8122786304604486</v>
-      </c>
-      <c r="X4">
-        <v>0.1515860115539986</v>
-      </c>
-      <c r="Y4">
-        <v>0.6606926189064499</v>
-      </c>
-      <c r="Z4">
-        <v>0.8191610586742921</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.1065058700501523</v>
-      </c>
-      <c r="AC4">
-        <v>-0.1065058700501523</v>
-      </c>
-      <c r="AD4">
-        <v>563.6</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>563.6</v>
-      </c>
-      <c r="AG4">
-        <v>-1067.9</v>
-      </c>
-      <c r="AH4">
-        <v>0.6881562881562882</v>
-      </c>
-      <c r="AI4">
-        <v>0.5051084423731851</v>
-      </c>
-      <c r="AJ4">
-        <v>1.314338461538461</v>
-      </c>
-      <c r="AK4">
-        <v>2.070777583866589</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
         <v>0</v>
       </c>
     </row>
